--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324"/>
+    <workbookView windowWidth="22188" windowHeight="8604"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -80,13 +80,7 @@
     <t>Акжигитова Екатерина Александровна</t>
   </si>
   <si>
-    <t>Вар1</t>
-  </si>
-  <si>
     <t>Баркова Марина Владимировна</t>
-  </si>
-  <si>
-    <t>Вар2</t>
   </si>
   <si>
     <t>Говор Светлана Алексеевна</t>
@@ -4348,30 +4342,26 @@
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B2"/>
       <c r="F2" s="3"/>
       <c r="I2" s="3"/>
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
+      <c r="B3"/>
       <c r="F3" s="3"/>
       <c r="I3" s="3"/>
       <c r="N3" s="3"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
+      <c r="B4">
+        <v>100</v>
       </c>
       <c r="F4" s="3"/>
       <c r="I4" s="3"/>
@@ -4379,41 +4369,37 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
         <v>18</v>
       </c>
+      <c r="B5"/>
       <c r="F5" s="3"/>
       <c r="I5" s="3"/>
       <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
+      <c r="B6">
+        <v>100</v>
       </c>
       <c r="I6" s="3"/>
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
+      <c r="B7"/>
       <c r="I7" s="3"/>
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
+      <c r="B8">
+        <v>100</v>
       </c>
       <c r="F8" s="3"/>
       <c r="I8" s="3"/>
@@ -4422,70 +4408,60 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
+      <c r="B9"/>
       <c r="I9" s="3"/>
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
+      <c r="B10"/>
       <c r="I10" s="3"/>
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
+      <c r="B11"/>
       <c r="I11" s="3"/>
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
+      <c r="B12"/>
       <c r="I12" s="3"/>
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
+      <c r="B13"/>
       <c r="I13" s="3"/>
       <c r="N13" s="3"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
-      <c r="B14" t="s">
-        <v>16</v>
+      <c r="B14">
+        <v>100</v>
       </c>
       <c r="I14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" ht="15.15" spans="1:14">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
-      <c r="B15" t="s">
-        <v>18</v>
+      <c r="B15">
+        <v>100</v>
       </c>
       <c r="N15" s="3"/>
     </row>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -80,10 +80,19 @@
     <t>Акжигитова Екатерина Александровна</t>
   </si>
   <si>
+    <t>Вар1</t>
+  </si>
+  <si>
     <t>Баркова Марина Владимировна</t>
   </si>
   <si>
+    <t>Вар2</t>
+  </si>
+  <si>
     <t>Говор Светлана Алексеевна</t>
+  </si>
+  <si>
+    <t>Вар3</t>
   </si>
   <si>
     <t>Давыдовская Ульяна Артемовна</t>
@@ -4342,26 +4351,33 @@
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2"/>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
       <c r="F2" s="3"/>
       <c r="I2" s="3"/>
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3"/>
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
       <c r="F3" s="3"/>
       <c r="I3" s="3"/>
       <c r="N3" s="3"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
       </c>
       <c r="F4" s="3"/>
       <c r="I4" s="3"/>
@@ -4369,37 +4385,47 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5"/>
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="I5" s="3"/>
       <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
       </c>
       <c r="I6" s="3"/>
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="B7"/>
       <c r="I7" s="3"/>
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
       </c>
       <c r="F8" s="3"/>
       <c r="I8" s="3"/>
@@ -4408,60 +4434,76 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9"/>
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10"/>
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11"/>
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12"/>
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13"/>
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
       <c r="I13" s="3"/>
       <c r="N13" s="3"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>100</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
       </c>
       <c r="I14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" ht="15.15" spans="1:14">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>100</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
       </c>
       <c r="N15" s="3"/>
     </row>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8604"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -4351,7 +4351,7 @@
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="3"/>
@@ -4362,7 +4362,7 @@
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="3"/>
@@ -4376,7 +4376,11 @@
       <c r="B4">
         <v>100</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="3"/>
@@ -4387,7 +4391,7 @@
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="3"/>
@@ -4401,7 +4405,13 @@
       <c r="B6">
         <v>100</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="3"/>
@@ -4411,7 +4421,7 @@
       <c r="A7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="3"/>
@@ -4424,7 +4434,9 @@
       <c r="B8">
         <v>100</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="3"/>
@@ -4436,7 +4448,7 @@
       <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>18</v>
       </c>
       <c r="I9" s="3"/>
@@ -4446,7 +4458,7 @@
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="3"/>
@@ -4456,7 +4468,7 @@
       <c r="A11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>16</v>
       </c>
       <c r="I11" s="3"/>
@@ -4466,7 +4478,7 @@
       <c r="A12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="3"/>
@@ -4476,7 +4488,7 @@
       <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="3"/>
@@ -4489,7 +4501,9 @@
       <c r="B14">
         <v>100</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="3"/>
@@ -4502,7 +4516,9 @@
       <c r="B15">
         <v>100</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15" t="s">
         <v>18</v>
       </c>
       <c r="N15" s="3"/>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4286,7 +4286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.2222222222222" customWidth="1"/>
@@ -4351,10 +4351,9 @@
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3"/>
       <c r="I2" s="3"/>
       <c r="N2" s="3"/>
     </row>
@@ -4362,10 +4361,9 @@
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3"/>
       <c r="I3" s="3"/>
       <c r="N3" s="3"/>
     </row>
@@ -4379,11 +4377,9 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4"/>
-      <c r="E4" t="s">
+      <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="3"/>
       <c r="I4" s="3"/>
       <c r="N4" s="3"/>
     </row>
@@ -4391,10 +4387,9 @@
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3"/>
       <c r="I5" s="3"/>
       <c r="N5" s="3"/>
     </row>
@@ -4406,12 +4401,15 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="3"/>
@@ -4421,7 +4419,7 @@
       <c r="A7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="3"/>
@@ -4434,12 +4432,9 @@
       <c r="B8">
         <v>100</v>
       </c>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8" t="s">
+      <c r="F8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="3"/>
       <c r="I8" s="3"/>
       <c r="L8" s="5"/>
       <c r="N8" s="3"/>
@@ -4448,7 +4443,7 @@
       <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I9" s="3"/>
@@ -4458,7 +4453,7 @@
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="3"/>
@@ -4468,7 +4463,10 @@
       <c r="A11" t="s">
         <v>27</v>
       </c>
-      <c r="E11" t="s">
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I11" s="3"/>
@@ -4478,7 +4476,7 @@
       <c r="A12" t="s">
         <v>28</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="3"/>
@@ -4488,7 +4486,7 @@
       <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="3"/>
@@ -4501,9 +4499,7 @@
       <c r="B14">
         <v>100</v>
       </c>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14" t="s">
+      <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="3"/>
@@ -4516,15 +4512,23 @@
       <c r="B15">
         <v>100</v>
       </c>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15" t="s">
+      <c r="F15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" ht="15.15" spans="1:1">
+    <row r="16" ht="15.15" spans="1:6">
       <c r="A16" s="4"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="6:6">
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="6:6">
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="6:6">
+      <c r="F19" s="3"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B15" etc:filterBottomFollowUsedRange="0">

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324"/>
+    <workbookView windowWidth="22188" windowHeight="8604"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -80,19 +80,10 @@
     <t>Акжигитова Екатерина Александровна</t>
   </si>
   <si>
-    <t>Вар1</t>
-  </si>
-  <si>
     <t>Баркова Марина Владимировна</t>
   </si>
   <si>
-    <t>Вар2</t>
-  </si>
-  <si>
     <t>Говор Светлана Алексеевна</t>
-  </si>
-  <si>
-    <t>Вар3</t>
   </si>
   <si>
     <t>Давыдовская Ульяна Артемовна</t>
@@ -4351,25 +4342,21 @@
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="I2" s="3"/>
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="I3" s="3"/>
       <c r="N3" s="3"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -4377,25 +4364,29 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>20</v>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
       </c>
       <c r="I4" s="3"/>
       <c r="N4" s="3"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="F5" s="3"/>
       <c r="I5" s="3"/>
       <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4409,112 +4400,99 @@
       <c r="E6">
         <v>100</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
+      <c r="F6" s="3">
+        <v>110</v>
       </c>
       <c r="I6" s="3"/>
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="F7" s="3"/>
       <c r="I7" s="3"/>
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="I8" s="3"/>
       <c r="L8" s="5"/>
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="I9" s="3"/>
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="I10" s="3"/>
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>16</v>
+      <c r="F11" s="3">
+        <v>100</v>
       </c>
       <c r="I11" s="3"/>
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="I12" s="3"/>
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="F13" s="3"/>
       <c r="I13" s="3"/>
       <c r="N13" s="3"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
+      <c r="C14">
+        <v>100</v>
       </c>
+      <c r="F14" s="3"/>
       <c r="I14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" ht="15.15" spans="1:14">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>100</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="F15" s="3"/>
       <c r="N15" s="3"/>
     </row>
     <row r="16" ht="15.15" spans="1:6">

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8604"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -306,13 +306,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBBBBB"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFBBBBBB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -781,10 +781,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -4338,7 +4338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -4346,7 +4346,7 @@
       <c r="I2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -4354,7 +4354,7 @@
       <c r="I3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4372,11 +4372,17 @@
       </c>
       <c r="F4" s="3">
         <v>100</v>
+      </c>
+      <c r="G4">
+        <v>90</v>
+      </c>
+      <c r="H4">
+        <v>80</v>
       </c>
       <c r="I4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4384,7 +4390,7 @@
       <c r="I5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4402,11 +4408,17 @@
       </c>
       <c r="F6" s="3">
         <v>110</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
       </c>
       <c r="I6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4414,7 +4426,7 @@
       <c r="I7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -4423,10 +4435,10 @@
       </c>
       <c r="F8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="4"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -4434,7 +4446,7 @@
       <c r="I9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -4442,7 +4454,7 @@
       <c r="I10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -4455,7 +4467,7 @@
       <c r="I11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -4463,7 +4475,7 @@
       <c r="I12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -4471,7 +4483,7 @@
       <c r="I13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -4485,7 +4497,7 @@
       <c r="I14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" ht="15.15" spans="1:15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -4495,8 +4507,8 @@
       <c r="F15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" ht="15.15" spans="1:6">
-      <c r="A16" s="4"/>
+    <row r="16" ht="15.15" spans="1:15">
+      <c r="A16" s="5"/>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="6:6">

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>Name</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>HW_7</t>
+  </si>
+  <si>
+    <t>HW_8</t>
   </si>
   <si>
     <t>Summary_HW</t>
@@ -80,10 +83,19 @@
     <t>Акжигитова Екатерина Александровна</t>
   </si>
   <si>
+    <t>вар1</t>
+  </si>
+  <si>
     <t>Баркова Марина Владимировна</t>
   </si>
   <si>
+    <t>вар2</t>
+  </si>
+  <si>
     <t>Говор Светлана Алексеевна</t>
+  </si>
+  <si>
+    <t>вар3</t>
   </si>
   <si>
     <t>Давыдовская Ульяна Артемовна</t>
@@ -4277,21 +4289,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="8.22222222222222" customWidth="1"/>
     <col min="3" max="6" width="6" customWidth="1"/>
-    <col min="9" max="9" width="13.8888888888889" customWidth="1"/>
-    <col min="10" max="10" width="8.22222222222222" customWidth="1"/>
-    <col min="11" max="11" width="13.2222222222222" customWidth="1"/>
-    <col min="13" max="13" width="13.1111111111111" customWidth="1"/>
-    <col min="14" max="14" width="17.1111111111111" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="10" max="10" width="13.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="8.22222222222222" customWidth="1"/>
+    <col min="12" max="12" width="13.2222222222222" customWidth="1"/>
+    <col min="14" max="14" width="13.1111111111111" customWidth="1"/>
+    <col min="15" max="15" width="17.1111111111111" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4319,44 +4331,53 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -4379,20 +4400,26 @@
       <c r="H4">
         <v>80</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="N4" s="3"/>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="N5" s="3"/>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4415,48 +4442,63 @@
       <c r="H6">
         <v>100</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="N6" s="3"/>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="O6" s="3"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>100</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="L8" s="4"/>
-      <c r="N8" s="3"/>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="M8" s="4"/>
+      <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="N9" s="3"/>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="O9" s="3"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="N10" s="3"/>
+      <c r="I10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="O10" s="3"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4464,28 +4506,37 @@
       <c r="F11" s="3">
         <v>100</v>
       </c>
-      <c r="I11" s="3"/>
-      <c r="N11" s="3"/>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="N12" s="3"/>
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="O12" s="3"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="N13" s="3"/>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4494,20 +4545,26 @@
         <v>100</v>
       </c>
       <c r="F14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="N14" s="3"/>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="O14" s="3"/>
     </row>
-    <row r="15" ht="15.15" spans="1:15">
+    <row r="15" ht="15.15" spans="1:16">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>100</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="N15" s="3"/>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15" s="3"/>
     </row>
-    <row r="16" ht="15.15" spans="1:15">
+    <row r="16" ht="15.15" spans="1:16">
       <c r="A16" s="5"/>
       <c r="F16" s="3"/>
     </row>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>Name</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>HW_8</t>
+  </si>
+  <si>
+    <t>HW_9_the_Last</t>
   </si>
   <si>
     <t>Summary_HW</t>
@@ -101,16 +104,31 @@
     <t>Давыдовская Ульяна Артемовна</t>
   </si>
   <si>
+    <t>вар4</t>
+  </si>
+  <si>
     <t>Ким София Германовна</t>
+  </si>
+  <si>
+    <t>вар5</t>
   </si>
   <si>
     <t>Костромин Архип Артурович</t>
   </si>
   <si>
+    <t>вар6</t>
+  </si>
+  <si>
     <t>Маркова Мария Александровна</t>
   </si>
   <si>
+    <t>вар7</t>
+  </si>
+  <si>
     <t>Морозова Полина Дмитриевна</t>
+  </si>
+  <si>
+    <t>вар8</t>
   </si>
   <si>
     <t>Орлянская Майя Константиновна</t>
@@ -4289,21 +4307,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="8.22222222222222" customWidth="1"/>
     <col min="3" max="6" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.8888888888889" customWidth="1"/>
-    <col min="11" max="11" width="8.22222222222222" customWidth="1"/>
-    <col min="12" max="12" width="13.2222222222222" customWidth="1"/>
-    <col min="14" max="14" width="13.1111111111111" customWidth="1"/>
-    <col min="15" max="15" width="17.1111111111111" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="10" max="10" width="15.2222222222222" customWidth="1"/>
+    <col min="11" max="11" width="13.8888888888889" customWidth="1"/>
+    <col min="12" max="12" width="8.22222222222222" customWidth="1"/>
+    <col min="13" max="13" width="13.2222222222222" customWidth="1"/>
+    <col min="15" max="15" width="13.1111111111111" customWidth="1"/>
+    <col min="16" max="16" width="17.1111111111111" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4334,50 +4353,53 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="O2" s="3"/>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -4400,26 +4422,27 @@
       <c r="H4">
         <v>80</v>
       </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="I4"/>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="I5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4442,63 +4465,66 @@
       <c r="H6">
         <v>100</v>
       </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="I7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>100</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="I8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="M8" s="4"/>
-      <c r="O8" s="3"/>
+      <c r="J8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="N8" s="4"/>
+      <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="I10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="O10" s="3"/>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4506,37 +4532,37 @@
       <c r="F11" s="3">
         <v>100</v>
       </c>
-      <c r="I11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3"/>
-      <c r="I12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="I13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="O13" s="3"/>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4545,26 +4571,26 @@
         <v>100</v>
       </c>
       <c r="F14" s="3"/>
-      <c r="I14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="P14" s="3"/>
     </row>
-    <row r="15" ht="15.15" spans="1:16">
+    <row r="15" ht="15.15" spans="1:17">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B15">
         <v>100</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
-      <c r="O15" s="3"/>
+      <c r="J15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="3"/>
     </row>
-    <row r="16" ht="15.15" spans="1:16">
+    <row r="16" ht="15.15" spans="1:17">
       <c r="A16" s="5"/>
       <c r="F16" s="3"/>
     </row>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324"/>
+    <workbookView windowWidth="22188" windowHeight="9264"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -62,10 +62,10 @@
     <t>HW_9_the_Last</t>
   </si>
   <si>
-    <t>Summary_HW</t>
+    <t>Summary_HW_Exam</t>
   </si>
   <si>
-    <t>Projects</t>
+    <t>Projects_ID</t>
   </si>
   <si>
     <t>Summary_Project</t>
@@ -86,49 +86,25 @@
     <t>Акжигитова Екатерина Александровна</t>
   </si>
   <si>
-    <t>вар1</t>
-  </si>
-  <si>
     <t>Баркова Марина Владимировна</t>
-  </si>
-  <si>
-    <t>вар2</t>
   </si>
   <si>
     <t>Говор Светлана Алексеевна</t>
   </si>
   <si>
-    <t>вар3</t>
-  </si>
-  <si>
     <t>Давыдовская Ульяна Артемовна</t>
-  </si>
-  <si>
-    <t>вар4</t>
   </si>
   <si>
     <t>Ким София Германовна</t>
   </si>
   <si>
-    <t>вар5</t>
-  </si>
-  <si>
     <t>Костромин Архип Артурович</t>
-  </si>
-  <si>
-    <t>вар6</t>
   </si>
   <si>
     <t>Маркова Мария Александровна</t>
   </si>
   <si>
-    <t>вар7</t>
-  </si>
-  <si>
     <t>Морозова Полина Дмитриевна</t>
-  </si>
-  <si>
-    <t>вар8</t>
   </si>
   <si>
     <t>Орлянская Майя Константиновна</t>
@@ -4315,7 +4291,7 @@
     <col min="3" max="6" width="6" customWidth="1"/>
     <col min="10" max="10" width="15.2222222222222" customWidth="1"/>
     <col min="11" max="11" width="13.8888888888889" customWidth="1"/>
-    <col min="12" max="12" width="8.22222222222222" customWidth="1"/>
+    <col min="12" max="12" width="11.1111111111111" customWidth="1"/>
     <col min="13" max="13" width="13.2222222222222" customWidth="1"/>
     <col min="15" max="15" width="13.1111111111111" customWidth="1"/>
     <col min="16" max="16" width="17.1111111111111" customWidth="1"/>
@@ -4380,26 +4356,32 @@
         <v>17</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="3"/>
+      <c r="K2" s="3">
+        <f>SUM(B2:J2)/900*100*0.2</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
       <c r="P2" s="3"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <f t="shared" ref="K3:K15" si="0">SUM(B3:J3)/900*100*0.2</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
       <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -4422,27 +4404,38 @@
       <c r="H4">
         <v>80</v>
       </c>
-      <c r="I4"/>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="3"/>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4" s="3">
+        <f t="shared" si="0"/>
+        <v>18.8888888888889</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
       <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
       <c r="P5" s="3"/>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4468,63 +4461,81 @@
       <c r="I6">
         <v>100</v>
       </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="3"/>
+      <c r="J6">
+        <v>90</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" si="0"/>
+        <v>21.1111111111111</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>6</v>
+      </c>
       <c r="P7" s="3"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>100</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="J8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <f t="shared" si="0"/>
+        <v>2.22222222222222</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
       <c r="N8" s="4"/>
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="J9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
       <c r="P9" s="3"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
       <c r="P10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4532,37 +4543,46 @@
       <c r="F11" s="3">
         <v>100</v>
       </c>
-      <c r="J11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <f t="shared" si="0"/>
+        <v>4.44444444444444</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
       <c r="P11" s="3"/>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3"/>
-      <c r="J12" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>3</v>
+      </c>
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4571,22 +4591,29 @@
         <v>100</v>
       </c>
       <c r="F14" s="3"/>
-      <c r="J14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <f t="shared" si="0"/>
+        <v>4.44444444444444</v>
+      </c>
+      <c r="L14">
+        <v>5</v>
+      </c>
       <c r="P14" s="3"/>
     </row>
     <row r="15" ht="15.15" spans="1:17">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>100</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="J15" t="s">
-        <v>28</v>
+      <c r="K15" s="3">
+        <f t="shared" si="0"/>
+        <v>2.22222222222222</v>
+      </c>
+      <c r="L15">
+        <v>6</v>
       </c>
       <c r="P15" s="3"/>
     </row>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -793,55 +793,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4590,10 +4590,30 @@
       <c r="C14">
         <v>100</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>100</v>
+      </c>
       <c r="K14" s="3">
         <f t="shared" si="0"/>
-        <v>4.44444444444444</v>
+        <v>20</v>
       </c>
       <c r="L14">
         <v>5</v>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9264"/>
+    <workbookView windowWidth="22188" windowHeight="8664"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -4627,13 +4627,39 @@
       <c r="B15">
         <v>100</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="C15">
+        <v>150</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
       <c r="K15" s="3">
         <f t="shared" si="0"/>
-        <v>2.22222222222222</v>
+        <v>21.1111111111111</v>
       </c>
       <c r="L15">
         <v>6</v>
+      </c>
+      <c r="M15">
+        <v>80</v>
       </c>
       <c r="P15" s="3"/>
     </row>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8664"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>Name</t>
   </si>
@@ -83,7 +83,13 @@
     <t>Final_Score</t>
   </si>
   <si>
+    <t>Final</t>
+  </si>
+  <si>
     <t>Акжигитова Екатерина Александровна</t>
+  </si>
+  <si>
+    <t>4-</t>
   </si>
   <si>
     <t>Баркова Марина Владимировна</t>
@@ -92,7 +98,13 @@
     <t>Говор Светлана Алексеевна</t>
   </si>
   <si>
+    <t>5-</t>
+  </si>
+  <si>
     <t>Давыдовская Ульяна Артемовна</t>
+  </si>
+  <si>
+    <t>не зачтено</t>
   </si>
   <si>
     <t>Ким София Германовна</t>
@@ -793,55 +805,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4283,7 +4295,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.2222222222222" customWidth="1"/>
@@ -4295,10 +4307,10 @@
     <col min="13" max="13" width="13.2222222222222" customWidth="1"/>
     <col min="15" max="15" width="13.1111111111111" customWidth="1"/>
     <col min="16" max="16" width="17.1111111111111" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="17" max="17" width="11.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4350,38 +4362,79 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="3"/>
       <c r="K2" s="3">
-        <f>SUM(B2:J2)/900*100*0.2</f>
+        <f>SUM(B2:J2)/900*100</f>
         <v>0</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
-      <c r="P2" s="3"/>
+      <c r="M2">
+        <v>100</v>
+      </c>
+      <c r="N2">
+        <v>11</v>
+      </c>
+      <c r="O2">
+        <f>N2/16*100</f>
+        <v>68.75</v>
+      </c>
+      <c r="P2" s="3">
+        <f>(K2+M2+O2)/3</f>
+        <v>56.25</v>
+      </c>
+      <c r="Q2">
+        <v>6</v>
+      </c>
+      <c r="R2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3"/>
       <c r="K3" s="3">
-        <f t="shared" ref="K3:K15" si="0">SUM(B3:J3)/900*100*0.2</f>
+        <f t="shared" ref="K3:K15" si="0">SUM(B3:J3)/900*100</f>
         <v>0</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
-      <c r="P3" s="3"/>
+      <c r="M3">
+        <v>100</v>
+      </c>
+      <c r="N3">
+        <v>11</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O15" si="1">N3/16*100</f>
+        <v>68.75</v>
+      </c>
+      <c r="P3" s="3">
+        <f t="shared" ref="P3:P15" si="2">(K3+M3+O3)/3</f>
+        <v>56.25</v>
+      </c>
+      <c r="Q3">
+        <v>6</v>
+      </c>
+      <c r="R3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -4412,16 +4465,35 @@
       </c>
       <c r="K4" s="3">
         <f t="shared" si="0"/>
-        <v>18.8888888888889</v>
+        <v>94.4444444444444</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="M4">
+        <v>60</v>
+      </c>
+      <c r="N4">
+        <v>10</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="P4" s="3">
+        <f t="shared" si="2"/>
+        <v>72.3148148148148</v>
+      </c>
+      <c r="Q4">
+        <v>8</v>
+      </c>
+      <c r="R4" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" s="3"/>
       <c r="K5" s="3">
@@ -4431,11 +4503,24 @@
       <c r="L5">
         <v>4</v>
       </c>
-      <c r="P5" s="3"/>
+      <c r="O5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4466,16 +4551,35 @@
       </c>
       <c r="K6" s="3">
         <f t="shared" si="0"/>
-        <v>21.1111111111111</v>
+        <v>105.555555555556</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="M6">
+        <v>90</v>
+      </c>
+      <c r="N6">
+        <v>11</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>68.75</v>
+      </c>
+      <c r="P6" s="3">
+        <f t="shared" si="2"/>
+        <v>88.1018518518518</v>
+      </c>
+      <c r="Q6">
+        <v>9</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3"/>
       <c r="K7" s="3">
@@ -4485,11 +4589,24 @@
       <c r="L7">
         <v>6</v>
       </c>
-      <c r="P7" s="3"/>
+      <c r="O7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -4497,17 +4614,35 @@
       <c r="F8" s="3"/>
       <c r="K8" s="3">
         <f t="shared" si="0"/>
-        <v>2.22222222222222</v>
+        <v>11.1111111111111</v>
       </c>
       <c r="L8">
         <v>7</v>
       </c>
-      <c r="N8" s="4"/>
-      <c r="P8" s="3"/>
+      <c r="M8">
+        <v>80</v>
+      </c>
+      <c r="N8" s="4">
+        <v>11</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>68.75</v>
+      </c>
+      <c r="P8" s="3">
+        <f t="shared" si="2"/>
+        <v>53.287037037037</v>
+      </c>
+      <c r="Q8">
+        <v>6</v>
+      </c>
+      <c r="R8" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3"/>
       <c r="K9" s="3">
@@ -4517,11 +4652,24 @@
       <c r="L9">
         <v>8</v>
       </c>
-      <c r="P9" s="3"/>
+      <c r="O9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F10" s="3"/>
       <c r="K10" s="3">
@@ -4531,11 +4679,24 @@
       <c r="L10">
         <v>1</v>
       </c>
-      <c r="P10" s="3"/>
+      <c r="O10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4545,16 +4706,35 @@
       </c>
       <c r="K11" s="3">
         <f t="shared" si="0"/>
-        <v>4.44444444444444</v>
+        <v>22.2222222222222</v>
       </c>
       <c r="L11">
         <v>2</v>
       </c>
-      <c r="P11" s="3"/>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>12</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="P11" s="3">
+        <f t="shared" si="2"/>
+        <v>65.7407407407407</v>
+      </c>
+      <c r="Q11">
+        <v>7</v>
+      </c>
+      <c r="R11">
+        <v>4</v>
+      </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F12" s="3"/>
       <c r="K12" s="3">
@@ -4564,11 +4744,30 @@
       <c r="L12">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="M12">
+        <v>100</v>
+      </c>
+      <c r="N12">
+        <v>11</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="1"/>
+        <v>68.75</v>
+      </c>
+      <c r="P12" s="3">
+        <f t="shared" si="2"/>
+        <v>56.25</v>
+      </c>
+      <c r="Q12">
+        <v>6</v>
+      </c>
+      <c r="R12" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F13" s="3"/>
       <c r="K13" s="3">
@@ -4578,11 +4777,24 @@
       <c r="L13">
         <v>4</v>
       </c>
-      <c r="P13" s="3"/>
+      <c r="O13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>24</v>
+      </c>
+      <c r="R13" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4613,16 +4825,35 @@
       </c>
       <c r="K14" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14">
+        <v>12</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="P14" s="3">
+        <f t="shared" si="2"/>
+        <v>91.6666666666667</v>
+      </c>
+      <c r="Q14">
+        <v>10</v>
+      </c>
+      <c r="R14">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" ht="15.15" spans="1:17">
+    <row r="15" ht="15.15" spans="1:18">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -4653,7 +4884,7 @@
       </c>
       <c r="K15" s="3">
         <f t="shared" si="0"/>
-        <v>21.1111111111111</v>
+        <v>105.555555555556</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -4661,9 +4892,25 @@
       <c r="M15">
         <v>80</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="N15">
+        <v>10</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="P15" s="3">
+        <f t="shared" si="2"/>
+        <v>82.6851851851852</v>
+      </c>
+      <c r="Q15">
+        <v>9</v>
+      </c>
+      <c r="R15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" ht="15.15" spans="1:17">
+    <row r="16" ht="15.15" spans="1:18">
       <c r="A16" s="5"/>
       <c r="F16" s="3"/>
     </row>

--- a/data/Classes_2026.xlsx
+++ b/data/Classes_2026.xlsx
@@ -4307,7 +4307,7 @@
     <col min="13" max="13" width="13.2222222222222" customWidth="1"/>
     <col min="15" max="15" width="13.1111111111111" customWidth="1"/>
     <col min="16" max="16" width="17.1111111111111" customWidth="1"/>
-    <col min="17" max="17" width="11.1111111111111" customWidth="1"/>
+    <col min="17" max="18" width="11.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
